--- a/artfynd/A 32488-2026 artfynd.xlsx
+++ b/artfynd/A 32488-2026 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>136359925</v>
       </c>
       <c r="B10" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136361308</v>
       </c>
       <c r="B11" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32488-2026 artfynd.xlsx
+++ b/artfynd/A 32488-2026 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>136359925</v>
       </c>
       <c r="B10" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136361308</v>
       </c>
       <c r="B11" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32488-2026 artfynd.xlsx
+++ b/artfynd/A 32488-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136359445</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136360315</v>
       </c>
       <c r="B3" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>136359925</v>
       </c>
       <c r="B10" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136361308</v>
       </c>
       <c r="B11" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32488-2026 artfynd.xlsx
+++ b/artfynd/A 32488-2026 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>136359925</v>
       </c>
       <c r="B10" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136361308</v>
       </c>
       <c r="B11" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32488-2026 artfynd.xlsx
+++ b/artfynd/A 32488-2026 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>136359925</v>
       </c>
       <c r="B10" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136361308</v>
       </c>
       <c r="B11" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32488-2026 artfynd.xlsx
+++ b/artfynd/A 32488-2026 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>136359925</v>
       </c>
       <c r="B10" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136361308</v>
       </c>
       <c r="B11" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
